--- a/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 44,08</t>
+          <t>26,49; 43,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,52; 54,44</t>
+          <t>34,64; 54,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,9; 41,57</t>
+          <t>22,65; 42,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 30,08</t>
+          <t>16,69; 31,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 44,41</t>
+          <t>27,4; 44,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,94; 58,36</t>
+          <t>39,49; 58,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 54,51</t>
+          <t>36,31; 54,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 35,09</t>
+          <t>19,54; 36,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,02; 41,17</t>
+          <t>30,1; 41,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,64; 54,04</t>
+          <t>39,15; 53,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,82; 46,82</t>
+          <t>32,59; 45,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 30,56</t>
+          <t>20,32; 31,16</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,96; 41,81</t>
+          <t>24,76; 41,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 43,42</t>
+          <t>24,75; 44,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 31,54</t>
+          <t>16,05; 31,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 38,98</t>
+          <t>21,8; 39,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,1; 48,48</t>
+          <t>29,25; 48,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,45; 64,46</t>
+          <t>46,8; 65,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 46,66</t>
+          <t>30,29; 46,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,26; 50,79</t>
+          <t>31,76; 50,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 42,71</t>
+          <t>29,35; 42,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,96; 51,93</t>
+          <t>38,62; 52,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 37,53</t>
+          <t>25,53; 36,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 42,53</t>
+          <t>29,89; 42,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,04; 42,95</t>
+          <t>22,99; 42,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,54; 45,72</t>
+          <t>25,7; 44,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,3; 42,15</t>
+          <t>20,6; 41,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,48; 46,71</t>
+          <t>24,06; 49,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,03; 58,9</t>
+          <t>41,19; 58,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,42; 59,72</t>
+          <t>38,15; 59,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 57,99</t>
+          <t>35,31; 56,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 56,36</t>
+          <t>32,15; 57,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,63; 50,02</t>
+          <t>36,7; 49,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,6; 49,06</t>
+          <t>33,77; 48,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 46,19</t>
+          <t>32,23; 47,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,65; 49,12</t>
+          <t>31,11; 49,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 44,19</t>
+          <t>31,87; 44,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,11; 50,6</t>
+          <t>37,0; 50,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,95; 47,35</t>
+          <t>34,19; 46,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 38,22</t>
+          <t>19,24; 38,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,25; 54,62</t>
+          <t>42,3; 55,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,66; 60,64</t>
+          <t>47,98; 60,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 47,19</t>
+          <t>34,07; 47,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,39; 52,43</t>
+          <t>36,74; 53,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,97; 47,79</t>
+          <t>38,86; 47,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,9; 53,86</t>
+          <t>44,74; 53,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,73; 45,37</t>
+          <t>36,48; 45,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,58; 43,29</t>
+          <t>29,33; 43,21</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,72; 51,76</t>
+          <t>34,63; 51,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,26; 56,3</t>
+          <t>40,9; 56,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,55; 43,86</t>
+          <t>30,31; 45,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,34; 43,46</t>
+          <t>25,7; 43,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,99; 49,68</t>
+          <t>34,76; 50,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,59; 51,71</t>
+          <t>34,68; 51,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,81; 55,54</t>
+          <t>39,64; 54,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 47,84</t>
+          <t>29,41; 48,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,05; 48,53</t>
+          <t>38,14; 49,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,45; 51,71</t>
+          <t>40,24; 51,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,62; 47,28</t>
+          <t>37,55; 47,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,19; 43,57</t>
+          <t>30,44; 43,35</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,21; 36,39</t>
+          <t>19,15; 35,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,58; 56,59</t>
+          <t>31,14; 56,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,5; 46,79</t>
+          <t>23,25; 45,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 26,72</t>
+          <t>9,56; 26,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,45; 65,56</t>
+          <t>45,72; 66,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,31; 62,76</t>
+          <t>39,39; 61,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,57; 59,23</t>
+          <t>38,55; 60,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,37; 48,31</t>
+          <t>25,41; 46,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,53; 47,72</t>
+          <t>32,96; 47,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,83; 56,7</t>
+          <t>40,41; 56,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,7; 50,18</t>
+          <t>33,78; 49,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 34,4</t>
+          <t>19,16; 33,77</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,94; 38,86</t>
+          <t>32,74; 39,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,71; 45,72</t>
+          <t>38,68; 45,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,06; 37,91</t>
+          <t>31,47; 38,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,1; 32,44</t>
+          <t>24,03; 32,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,75; 48,77</t>
+          <t>42,05; 48,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,54; 54,72</t>
+          <t>47,34; 54,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,39; 47,5</t>
+          <t>40,53; 47,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,11; 42,95</t>
+          <t>35,49; 43,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,51; 43,07</t>
+          <t>38,43; 43,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,16; 49,22</t>
+          <t>43,87; 49,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,87; 42,02</t>
+          <t>36,94; 41,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,81; 36,95</t>
+          <t>31,0; 37,1</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30802</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30644</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18705</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21161</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30491</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30649</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33877</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>30579</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>61294</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61293</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>51740</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>23228; 38325</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23923; 37867</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13441; 25296</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15500; 29599</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23026; 37647</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24681; 36691</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26923; 40426</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>21654; 39965</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>51694; 71548</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>51511; 71037</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>43503; 61181</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>41394; 63477</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24265</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23389</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18584</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25296</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26163</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42949</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35371</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36136</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>50428</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>66338</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53954</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>61432</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>18312; 31025</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17195; 30703</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12880; 25472</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18411; 33027</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20063; 32963</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36034; 50547</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28174; 43039</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>27828; 44412</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>41843; 61033</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>56569; 76308</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>44224; 63933</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>51446; 73013</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22507</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14791</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30954</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28651</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24564</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>62636</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53461</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>43442</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>38930</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12955; 23877</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16687; 29067</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10152; 20548</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10014; 20440</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36176; 51726</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23990; 37580</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21822; 35051</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>17946; 32221</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>52915; 71955</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>43163; 61798</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>35800; 52618</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>30312; 48198</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>63681</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62181</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69027</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59533</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80996</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93644</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64800</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>81855</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>144676</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>155825</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>133827</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>141388</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>53273; 73559</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>53001; 71781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57749; 78847</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37532; 75979</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>70677; 92258</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>82779; 105203</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>54256; 75125</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>67477; 97797</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>129903; 159011</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>141278; 170080</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>119719; 148649</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>111103; 163689</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>38264</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>55904</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40625</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32361</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47207</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54159</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>54330</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>85471</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98055</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>94784</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>86691</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>30902; 46019</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46883; 65296</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33412; 50044</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24632; 41692</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38397; 55554</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34031; 50824</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>44889; 62178</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>40843; 67450</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>76163; 98186</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>85616; 109767</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>83897; 107177</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>71440; 101751</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>18130</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18249</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16268</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9869</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32082</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29242</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>26593</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>23527</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>50212</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>47491</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>42861</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>33396</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>12925; 24269</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12863; 23353</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11090; 21917</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5703; 15564</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26320; 38120</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22580; 35365</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>21064; 32878</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>16876; 30786</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>41222; 59130</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>39863; 55745</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>34574; 50773</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>24158; 42577</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>193385</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>212875</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>177999</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>162586</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>261332</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>269588</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>243450</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>250991</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>454717</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>482463</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>421449</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>413577</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>177411; 212300</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>194450; 230122</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>162289; 197523</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>136858; 184336</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>242025; 279837</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>251076; 288749</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>225412; 262879</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>228255; 278306</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>429387; 481067</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>453130; 508181</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>395956; 447030</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>376016; 449958</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 43,71</t>
+          <t>26,74; 42,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,64; 54,82</t>
+          <t>34,11; 53,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 42,62</t>
+          <t>22,42; 41,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 31,87</t>
+          <t>16,29; 30,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,4; 44,8</t>
+          <t>28,28; 44,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,49; 58,71</t>
+          <t>39,01; 59,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 54,52</t>
+          <t>36,32; 54,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 36,06</t>
+          <t>19,26; 35,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 41,67</t>
+          <t>29,64; 41,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,15; 53,99</t>
+          <t>39,66; 53,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,59; 45,83</t>
+          <t>32,16; 46,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,32; 31,16</t>
+          <t>20,2; 31,34</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 41,95</t>
+          <t>24,23; 41,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,75; 44,19</t>
+          <t>25,42; 43,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 31,75</t>
+          <t>16,3; 31,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 39,1</t>
+          <t>22,35; 38,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,25; 48,05</t>
+          <t>29,88; 48,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,8; 65,65</t>
+          <t>47,06; 65,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,29; 46,27</t>
+          <t>29,97; 46,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,76; 50,68</t>
+          <t>31,89; 50,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,35; 42,81</t>
+          <t>28,56; 42,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 52,1</t>
+          <t>38,97; 52,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,53; 36,9</t>
+          <t>25,02; 36,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,89; 42,43</t>
+          <t>29,36; 42,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,99; 42,37</t>
+          <t>22,28; 42,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,7; 44,77</t>
+          <t>25,88; 43,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 41,69</t>
+          <t>20,38; 41,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,06; 49,12</t>
+          <t>23,15; 47,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,19; 58,9</t>
+          <t>42,11; 58,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 59,76</t>
+          <t>38,84; 59,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 56,71</t>
+          <t>36,16; 56,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 57,73</t>
+          <t>31,87; 57,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,7; 49,91</t>
+          <t>37,37; 50,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,77; 48,35</t>
+          <t>35,47; 48,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,23; 47,36</t>
+          <t>31,48; 46,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,11; 49,47</t>
+          <t>30,89; 48,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 44,0</t>
+          <t>31,99; 44,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 50,12</t>
+          <t>36,83; 50,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,19; 46,68</t>
+          <t>34,62; 47,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,24; 38,94</t>
+          <t>19,64; 38,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 55,22</t>
+          <t>42,47; 54,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,98; 60,98</t>
+          <t>48,17; 60,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,07; 47,17</t>
+          <t>34,08; 46,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,74; 53,25</t>
+          <t>37,5; 52,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,86; 47,57</t>
+          <t>38,69; 47,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 53,86</t>
+          <t>44,87; 53,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,48; 45,3</t>
+          <t>36,15; 45,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,33; 43,21</t>
+          <t>28,82; 43,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 51,57</t>
+          <t>35,16; 52,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,9; 56,97</t>
+          <t>40,72; 56,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,31; 45,4</t>
+          <t>29,87; 44,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,7; 43,5</t>
+          <t>26,2; 43,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,76; 50,3</t>
+          <t>35,8; 49,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,68; 51,8</t>
+          <t>34,02; 51,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,64; 54,91</t>
+          <t>40,44; 55,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 48,57</t>
+          <t>29,19; 48,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,14; 49,17</t>
+          <t>36,8; 48,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,24; 51,6</t>
+          <t>40,69; 52,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,55; 47,96</t>
+          <t>37,13; 48,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,44; 43,35</t>
+          <t>30,66; 43,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,15; 35,96</t>
+          <t>18,35; 35,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,14; 56,53</t>
+          <t>32,02; 57,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,25; 45,95</t>
+          <t>23,38; 46,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 26,09</t>
+          <t>9,66; 26,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,72; 66,21</t>
+          <t>45,32; 65,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,39; 61,69</t>
+          <t>40,51; 62,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,55; 60,16</t>
+          <t>37,7; 59,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,41; 46,35</t>
+          <t>25,25; 46,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,96; 47,28</t>
+          <t>33,51; 47,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40,41; 56,52</t>
+          <t>39,96; 56,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,78; 49,61</t>
+          <t>33,76; 49,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,16; 33,77</t>
+          <t>19,75; 33,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 39,18</t>
+          <t>32,16; 38,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,68; 45,78</t>
+          <t>38,77; 45,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,47; 38,3</t>
+          <t>31,42; 38,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,03; 32,37</t>
+          <t>23,53; 32,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,05; 48,62</t>
+          <t>42,18; 48,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,34; 54,45</t>
+          <t>46,88; 54,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,53; 47,27</t>
+          <t>40,56; 47,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,49; 43,27</t>
+          <t>34,83; 43,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,43; 43,05</t>
+          <t>38,34; 43,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,87; 49,19</t>
+          <t>43,96; 49,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,94; 41,71</t>
+          <t>36,49; 41,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,0; 37,1</t>
+          <t>31,0; 37,05</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23228; 38325</t>
+          <t>23443; 37623</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23923; 37867</t>
+          <t>23560; 37197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13441; 25296</t>
+          <t>13306; 24762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15500; 29599</t>
+          <t>15128; 27926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23026; 37647</t>
+          <t>23764; 37701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24681; 36691</t>
+          <t>24378; 37045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26923; 40426</t>
+          <t>26929; 40417</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21654; 39965</t>
+          <t>21340; 39444</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51694; 71548</t>
+          <t>50894; 71425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51511; 71037</t>
+          <t>52178; 70362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43503; 61181</t>
+          <t>42936; 62053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41394; 63477</t>
+          <t>41144; 63845</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18312; 31025</t>
+          <t>17922; 31048</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17195; 30703</t>
+          <t>17662; 30068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12880; 25472</t>
+          <t>13080; 25257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18411; 33027</t>
+          <t>18877; 32506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20063; 32963</t>
+          <t>20498; 33130</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36034; 50547</t>
+          <t>36230; 50395</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28174; 43039</t>
+          <t>27872; 43423</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27828; 44412</t>
+          <t>27946; 44665</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41843; 61033</t>
+          <t>40712; 60001</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56569; 76308</t>
+          <t>57077; 76503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44224; 63933</t>
+          <t>43344; 64019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51446; 73013</t>
+          <t>50524; 72589</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12955; 23877</t>
+          <t>12552; 24158</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16687; 29067</t>
+          <t>16806; 28549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10152; 20548</t>
+          <t>10044; 20326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10014; 20440</t>
+          <t>9634; 19769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36176; 51726</t>
+          <t>36981; 51359</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23990; 37580</t>
+          <t>24428; 37445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21822; 35051</t>
+          <t>22348; 34824</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17946; 32221</t>
+          <t>17791; 31991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52915; 71955</t>
+          <t>53880; 72269</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43163; 61798</t>
+          <t>45343; 62056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35800; 52618</t>
+          <t>34972; 52016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30312; 48198</t>
+          <t>30096; 47486</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53273; 73559</t>
+          <t>53487; 73999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53001; 71781</t>
+          <t>52757; 72526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57749; 78847</t>
+          <t>58466; 80207</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37532; 75979</t>
+          <t>38316; 76026</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70677; 92258</t>
+          <t>70952; 90478</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82779; 105203</t>
+          <t>83106; 105011</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54256; 75125</t>
+          <t>54274; 74226</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67477; 97797</t>
+          <t>68872; 96986</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129903; 159011</t>
+          <t>129340; 158628</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>141278; 170080</t>
+          <t>141674; 169828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119719; 148649</t>
+          <t>118631; 149075</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>111103; 163689</t>
+          <t>109150; 163461</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30902; 46019</t>
+          <t>31377; 46434</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46883; 65296</t>
+          <t>46674; 64769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33412; 50044</t>
+          <t>32922; 48810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24632; 41692</t>
+          <t>25113; 41940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38397; 55554</t>
+          <t>39542; 55105</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34031; 50824</t>
+          <t>33376; 50324</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44889; 62178</t>
+          <t>45787; 63369</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40843; 67450</t>
+          <t>40536; 66765</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76163; 98186</t>
+          <t>73494; 96375</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85616; 109767</t>
+          <t>86558; 110641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83897; 107177</t>
+          <t>82972; 107311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71440; 101751</t>
+          <t>71957; 101328</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12925; 24269</t>
+          <t>12386; 24149</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12863; 23353</t>
+          <t>13229; 23551</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11090; 21917</t>
+          <t>11153; 22404</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5703; 15564</t>
+          <t>5761; 15848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26320; 38120</t>
+          <t>26092; 37486</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22580; 35365</t>
+          <t>23226; 35972</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21064; 32878</t>
+          <t>20602; 32736</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16876; 30786</t>
+          <t>16775; 30849</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41222; 59130</t>
+          <t>41909; 59352</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39863; 55745</t>
+          <t>39419; 55728</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34574; 50773</t>
+          <t>34556; 50242</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24158; 42577</t>
+          <t>24902; 42392</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>177411; 212300</t>
+          <t>174278; 210117</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>194450; 230122</t>
+          <t>194869; 230500</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162289; 197523</t>
+          <t>162032; 196597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136858; 184336</t>
+          <t>134018; 184019</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>242025; 279837</t>
+          <t>242780; 281005</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>251076; 288749</t>
+          <t>248633; 288436</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>225412; 262879</t>
+          <t>225554; 263101</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>228255; 278306</t>
+          <t>224021; 277476</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>429387; 481067</t>
+          <t>428392; 481427</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>453130; 508181</t>
+          <t>454144; 509811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>395956; 447030</t>
+          <t>391088; 445110</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>376016; 449958</t>
+          <t>375980; 449333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49,04%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45,69%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28,68%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35,13%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31,52%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,69%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,74; 42,91</t>
+          <t>28,19; 44,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,11; 53,86</t>
+          <t>38,94; 58,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,42; 41,72</t>
+          <t>36,96; 54,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 30,07</t>
+          <t>20,74; 36,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,28; 44,86</t>
+          <t>27,57; 44,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,01; 59,28</t>
+          <t>34,52; 54,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,32; 54,51</t>
+          <t>21,9; 41,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,26; 35,59</t>
+          <t>16,34; 30,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,64; 41,59</t>
+          <t>30,02; 41,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,66; 53,48</t>
+          <t>39,64; 54,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,16; 46,48</t>
+          <t>32,82; 46,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 31,34</t>
+          <t>20,14; 31,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38,03%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>32,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>33,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>23,16%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 41,98</t>
+          <t>30,1; 48,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 43,27</t>
+          <t>46,45; 64,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 31,48</t>
+          <t>29,74; 46,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,35; 38,49</t>
+          <t>32,63; 51,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,88; 48,3</t>
+          <t>24,96; 41,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,06; 65,46</t>
+          <t>24,76; 43,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,97; 46,69</t>
+          <t>16,08; 31,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,89; 50,97</t>
+          <t>21,58; 38,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,56; 42,09</t>
+          <t>29,0; 42,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,97; 52,23</t>
+          <t>37,96; 51,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,02; 36,95</t>
+          <t>26,02; 37,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,36; 42,18</t>
+          <t>29,52; 42,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50,55%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>34,66%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>30,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,36%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,28; 42,87</t>
+          <t>42,03; 58,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,97</t>
+          <t>39,42; 59,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 41,24</t>
+          <t>37,52; 57,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,15; 47,51</t>
+          <t>33,21; 57,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,11; 58,48</t>
+          <t>23,04; 42,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,84; 59,54</t>
+          <t>25,54; 45,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,16; 56,35</t>
+          <t>20,3; 42,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 57,32</t>
+          <t>23,14; 46,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,37; 50,13</t>
+          <t>36,63; 50,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 48,55</t>
+          <t>34,6; 49,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,48; 46,82</t>
+          <t>32,15; 46,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,89; 48,74</t>
+          <t>31,23; 48,47</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44,29%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>38,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>43,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>40,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,99; 44,26</t>
+          <t>42,25; 54,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,83; 50,63</t>
+          <t>47,66; 60,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 47,49</t>
+          <t>34,61; 47,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,64; 38,96</t>
+          <t>37,13; 52,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,47; 54,15</t>
+          <t>32,07; 44,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,17; 60,87</t>
+          <t>37,11; 50,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 46,61</t>
+          <t>34,95; 47,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,5; 52,81</t>
+          <t>27,16; 39,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,69; 47,46</t>
+          <t>38,97; 47,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,87; 53,78</t>
+          <t>44,9; 53,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 45,43</t>
+          <t>36,73; 45,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,82; 43,15</t>
+          <t>34,47; 44,42</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42,96%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>42,88%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>48,77%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>36,86%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33,77%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>42,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,16; 52,04</t>
+          <t>34,99; 49,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,72; 56,51</t>
+          <t>35,59; 51,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 44,28</t>
+          <t>39,81; 55,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 43,76</t>
+          <t>29,22; 47,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,8; 49,89</t>
+          <t>34,72; 51,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,02; 51,29</t>
+          <t>40,26; 56,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,44; 55,96</t>
+          <t>29,55; 43,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,19; 48,08</t>
+          <t>23,98; 40,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,8; 48,26</t>
+          <t>37,05; 48,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,69; 52,01</t>
+          <t>40,45; 51,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,13; 48,02</t>
+          <t>36,62; 47,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 43,17</t>
+          <t>29,95; 42,92</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48,66%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26,87%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,35; 35,78</t>
+          <t>44,45; 65,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,02; 57,01</t>
+          <t>40,31; 62,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,38; 46,97</t>
+          <t>36,57; 59,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 26,57</t>
+          <t>26,68; 49,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,32; 65,11</t>
+          <t>19,21; 36,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,51; 62,75</t>
+          <t>32,58; 56,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,7; 59,9</t>
+          <t>23,5; 46,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,25; 46,44</t>
+          <t>8,84; 25,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,51; 47,46</t>
+          <t>33,53; 47,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,96; 56,5</t>
+          <t>39,83; 56,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,76; 49,09</t>
+          <t>33,7; 50,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,75; 33,63</t>
+          <t>19,83; 34,8</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50,83%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43,78%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>35,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42,35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>34,52%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,16; 38,78</t>
+          <t>41,75; 48,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,86</t>
+          <t>47,54; 54,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,42; 38,12</t>
+          <t>40,39; 47,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 32,31</t>
+          <t>35,56; 43,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,18; 48,82</t>
+          <t>31,94; 38,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,88; 54,39</t>
+          <t>38,71; 45,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,56; 47,31</t>
+          <t>31,06; 37,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,83; 43,14</t>
+          <t>25,41; 32,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,34; 43,08</t>
+          <t>38,51; 43,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,96; 49,35</t>
+          <t>44,16; 49,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,49; 41,53</t>
+          <t>36,87; 42,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,0; 37,05</t>
+          <t>31,85; 36,95</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30491</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30649</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33877</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28930</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>30802</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>30644</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>18705</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21161</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30491</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30649</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33877</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30579</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>49964</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23443; 37623</t>
+          <t>23689; 37322</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23560; 37197</t>
+          <t>24335; 36474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13306; 24762</t>
+          <t>27404; 40419</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15128; 27926</t>
+          <t>20915; 37238</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23764; 37701</t>
+          <t>24169; 38645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24378; 37045</t>
+          <t>23844; 37601</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26929; 40417</t>
+          <t>12998; 24675</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21340; 39444</t>
+          <t>14947; 27726</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50894; 71425</t>
+          <t>51549; 70692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52178; 70362</t>
+          <t>52159; 71099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42936; 62053</t>
+          <t>43817; 62503</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41144; 63845</t>
+          <t>38735; 60470</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35371</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24265</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18584</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25296</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26163</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42949</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35371</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>60778</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17922; 31048</t>
+          <t>20645; 33254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17662; 30068</t>
+          <t>35760; 49626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13080; 25257</t>
+          <t>27666; 43400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18877; 32506</t>
+          <t>27510; 43287</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20498; 33130</t>
+          <t>18463; 30923</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36230; 50395</t>
+          <t>17204; 30169</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27872; 43423</t>
+          <t>12897; 25305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27946; 44665</t>
+          <t>18607; 33422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40712; 60001</t>
+          <t>41341; 60882</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57077; 76503</t>
+          <t>55596; 76057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43344; 64019</t>
+          <t>45079; 65012</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50524; 72589</t>
+          <t>50340; 72466</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30954</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28651</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22189</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>18243</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>14791</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14366</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44393</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30954</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28651</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>36791</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12552; 24158</t>
+          <t>36913; 51731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16806; 28549</t>
+          <t>24787; 37557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10044; 20326</t>
+          <t>23187; 35842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9634; 19769</t>
+          <t>16601; 28823</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36981; 51359</t>
+          <t>12981; 24203</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24428; 37445</t>
+          <t>16584; 29686</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22348; 34824</t>
+          <t>10005; 20777</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17791; 31991</t>
+          <t>9920; 20103</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53880; 72269</t>
+          <t>52806; 72120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45343; 62056</t>
+          <t>44226; 62703</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34972; 52016</t>
+          <t>35713; 51317</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30096; 47486</t>
+          <t>29005; 45010</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>80996</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93644</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>64800</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76096</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>63681</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>62181</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>69027</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59533</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80996</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93644</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64800</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>141388</t>
+          <t>129827</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53487; 73999</t>
+          <t>70589; 91253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52757; 72526</t>
+          <t>82229; 104625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58466; 80207</t>
+          <t>55123; 75154</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38316; 76026</t>
+          <t>63793; 89736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70952; 90478</t>
+          <t>53616; 73885</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83106; 105011</t>
+          <t>53152; 72480</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54274; 74226</t>
+          <t>59035; 79972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68872; 96986</t>
+          <t>43617; 64138</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129340; 158628</t>
+          <t>130244; 159749</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>141674; 169828</t>
+          <t>141779; 170077</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118631; 149075</t>
+          <t>120534; 148889</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>109150; 163461</t>
+          <t>114590; 147655</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47207</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54159</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>49694</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>38264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>55904</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>40625</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32361</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47207</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54159</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54330</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86691</t>
+          <t>80167</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31377; 46434</t>
+          <t>38650; 54876</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46674; 64769</t>
+          <t>34921; 50738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32922; 48810</t>
+          <t>45083; 62885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25113; 41940</t>
+          <t>37387; 60961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>39542; 55105</t>
+          <t>30978; 46190</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33376; 50324</t>
+          <t>46146; 64538</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45787; 63369</t>
+          <t>32572; 48347</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40536; 66765</t>
+          <t>23059; 38817</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73494; 96375</t>
+          <t>73979; 96915</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86558; 110641</t>
+          <t>86045; 109999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82972; 107311</t>
+          <t>81837; 105659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71957; 101328</t>
+          <t>67114; 96192</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>32082</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29242</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26593</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>23668</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>18130</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>18249</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>16268</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9869</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>32082</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29242</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>26593</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33396</t>
+          <t>33308</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12386; 24149</t>
+          <t>25593; 37746</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13229; 23551</t>
+          <t>23109; 35980</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11153; 22404</t>
+          <t>19983; 32366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5761; 15848</t>
+          <t>16937; 31604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26092; 37486</t>
+          <t>12963; 24558</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23226; 35972</t>
+          <t>13461; 23379</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20602; 32736</t>
+          <t>11209; 22320</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16775; 30849</t>
+          <t>5447; 15529</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41909; 59352</t>
+          <t>41929; 59672</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39419; 55728</t>
+          <t>39284; 55924</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34556; 50242</t>
+          <t>34490; 51359</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24902; 42392</t>
+          <t>24797; 43523</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>233</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>261332</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>269588</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>243450</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>235732</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>193385</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>212875</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>177999</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>162586</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>261332</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>269588</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>243450</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>250991</t>
+          <t>155102</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>413577</t>
+          <t>390834</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>174278; 210117</t>
+          <t>240285; 280730</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>194869; 230500</t>
+          <t>252107; 290210</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162032; 196597</t>
+          <t>224624; 264139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134018; 184019</t>
+          <t>212777; 259160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>242780; 281005</t>
+          <t>173086; 210558</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>248633; 288436</t>
+          <t>194600; 229794</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>225554; 263101</t>
+          <t>160177; 195513</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>224021; 277476</t>
+          <t>136966; 173433</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>428392; 481427</t>
+          <t>430338; 481343</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>454144; 509811</t>
+          <t>456192; 508407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>391088; 445110</t>
+          <t>395216; 450316</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>375980; 449333</t>
+          <t>362249; 420215</t>
         </is>
       </c>
     </row>
